--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_aysen.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_aysen.xlsx
@@ -362,42 +362,42 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>E_PRENETA_a</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>E_BASNETA_a</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>E_MEDIANETA_a</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>E_SUPNETA_a</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>E_PREBRUT_a</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>E_PRENETA_a</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>E_BASBRUT_a</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>E_BASNETA_a</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>E_MEDIABRUT_a</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>E_MEDIANETA_a</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>E_SUPBRUT_a</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>E_SUPNETA_a</t>
         </is>
       </c>
     </row>
@@ -408,28 +408,28 @@
         </is>
       </c>
       <c r="B2">
+        <v>65.78997</v>
+      </c>
+      <c r="C2">
+        <v>96.63330000000001</v>
+      </c>
+      <c r="D2">
+        <v>76.03712</v>
+      </c>
+      <c r="E2">
+        <v>41.44527</v>
+      </c>
+      <c r="F2">
         <v>65.92339</v>
       </c>
-      <c r="C2">
-        <v>65.78997</v>
-      </c>
-      <c r="D2">
+      <c r="G2">
         <v>103.4967</v>
       </c>
-      <c r="E2">
-        <v>96.63330000000001</v>
-      </c>
-      <c r="F2">
+      <c r="H2">
         <v>104.8035</v>
       </c>
-      <c r="G2">
-        <v>76.03712</v>
-      </c>
-      <c r="H2">
+      <c r="I2">
         <v>66.3428</v>
-      </c>
-      <c r="I2">
-        <v>41.44527</v>
       </c>
     </row>
     <row r="3">
@@ -442,25 +442,25 @@
         <v>67.34694</v>
       </c>
       <c r="C3">
+        <v>96.875</v>
+      </c>
+      <c r="D3">
+        <v>85.29411</v>
+      </c>
+      <c r="E3">
+        <v>31.34328</v>
+      </c>
+      <c r="F3">
         <v>67.34694</v>
       </c>
-      <c r="D3">
+      <c r="G3">
         <v>102.0833</v>
       </c>
-      <c r="E3">
-        <v>96.875</v>
-      </c>
-      <c r="F3">
+      <c r="H3">
         <v>102.9412</v>
       </c>
-      <c r="G3">
-        <v>85.29411</v>
-      </c>
-      <c r="H3">
+      <c r="I3">
         <v>40.29851</v>
-      </c>
-      <c r="I3">
-        <v>31.34328</v>
       </c>
     </row>
     <row r="4">
@@ -470,28 +470,28 @@
         </is>
       </c>
       <c r="B4">
+        <v>67.24059</v>
+      </c>
+      <c r="C4">
+        <v>97.46117</v>
+      </c>
+      <c r="D4">
+        <v>76.76102</v>
+      </c>
+      <c r="E4">
+        <v>38.08261</v>
+      </c>
+      <c r="F4">
         <v>67.33122</v>
       </c>
-      <c r="C4">
-        <v>67.24059</v>
-      </c>
-      <c r="D4">
+      <c r="G4">
         <v>104.8686</v>
       </c>
-      <c r="E4">
-        <v>97.46117</v>
-      </c>
-      <c r="F4">
+      <c r="H4">
         <v>107.5708</v>
       </c>
-      <c r="G4">
-        <v>76.76102</v>
-      </c>
-      <c r="H4">
+      <c r="I4">
         <v>58.31754</v>
-      </c>
-      <c r="I4">
-        <v>38.08261</v>
       </c>
     </row>
     <row r="5">
@@ -501,28 +501,28 @@
         </is>
       </c>
       <c r="B5">
+        <v>70.44968</v>
+      </c>
+      <c r="C5">
+        <v>96.37096</v>
+      </c>
+      <c r="D5">
+        <v>77.3639</v>
+      </c>
+      <c r="E5">
+        <v>31.70255</v>
+      </c>
+      <c r="F5">
         <v>70.66381</v>
       </c>
-      <c r="C5">
-        <v>70.44968</v>
-      </c>
-      <c r="D5">
+      <c r="G5">
         <v>103.4946</v>
       </c>
-      <c r="E5">
-        <v>96.37096</v>
-      </c>
-      <c r="F5">
+      <c r="H5">
         <v>109.4556</v>
       </c>
-      <c r="G5">
-        <v>77.3639</v>
-      </c>
-      <c r="H5">
+      <c r="I5">
         <v>50.48923</v>
-      </c>
-      <c r="I5">
-        <v>31.70255</v>
       </c>
     </row>
     <row r="6">
@@ -535,25 +535,25 @@
         <v>75.18797000000001</v>
       </c>
       <c r="C6">
+        <v>97.66355</v>
+      </c>
+      <c r="D6">
+        <v>86.95652</v>
+      </c>
+      <c r="E6">
+        <v>36.41304</v>
+      </c>
+      <c r="F6">
         <v>75.18797000000001</v>
       </c>
-      <c r="D6">
+      <c r="G6">
         <v>103.271</v>
       </c>
-      <c r="E6">
-        <v>97.66355</v>
-      </c>
-      <c r="F6">
+      <c r="H6">
         <v>93.91304</v>
       </c>
-      <c r="G6">
-        <v>86.95652</v>
-      </c>
-      <c r="H6">
+      <c r="I6">
         <v>53.26087</v>
-      </c>
-      <c r="I6">
-        <v>36.41304</v>
       </c>
     </row>
     <row r="7">
@@ -563,28 +563,28 @@
         </is>
       </c>
       <c r="B7">
+        <v>75</v>
+      </c>
+      <c r="C7">
+        <v>96.54378</v>
+      </c>
+      <c r="D7">
+        <v>83.65385000000001</v>
+      </c>
+      <c r="E7">
+        <v>35.9375</v>
+      </c>
+      <c r="F7">
         <v>75.32468</v>
       </c>
-      <c r="C7">
-        <v>75</v>
-      </c>
-      <c r="D7">
+      <c r="G7">
         <v>100</v>
       </c>
-      <c r="E7">
-        <v>96.54378</v>
-      </c>
-      <c r="F7">
+      <c r="H7">
         <v>108.6538</v>
       </c>
-      <c r="G7">
-        <v>83.65385000000001</v>
-      </c>
-      <c r="H7">
+      <c r="I7">
         <v>50.78125</v>
-      </c>
-      <c r="I7">
-        <v>35.9375</v>
       </c>
     </row>
     <row r="8">
@@ -597,25 +597,25 @@
         <v>82.53968</v>
       </c>
       <c r="C8">
+        <v>97.59036</v>
+      </c>
+      <c r="D8">
+        <v>82.35294</v>
+      </c>
+      <c r="E8">
+        <v>19.51219</v>
+      </c>
+      <c r="F8">
         <v>82.53968</v>
       </c>
-      <c r="D8">
+      <c r="G8">
         <v>100</v>
       </c>
-      <c r="E8">
-        <v>97.59036</v>
-      </c>
-      <c r="F8">
+      <c r="H8">
         <v>94.11765</v>
       </c>
-      <c r="G8">
-        <v>82.35294</v>
-      </c>
-      <c r="H8">
+      <c r="I8">
         <v>56.09756</v>
-      </c>
-      <c r="I8">
-        <v>19.51219</v>
       </c>
     </row>
     <row r="9">
@@ -628,25 +628,25 @@
         <v>60.37736</v>
       </c>
       <c r="C9">
+        <v>97.33334000000001</v>
+      </c>
+      <c r="D9">
+        <v>82.75861999999999</v>
+      </c>
+      <c r="E9">
+        <v>34</v>
+      </c>
+      <c r="F9">
         <v>60.37736</v>
       </c>
-      <c r="D9">
+      <c r="G9">
         <v>100</v>
       </c>
-      <c r="E9">
-        <v>97.33334000000001</v>
-      </c>
-      <c r="F9">
+      <c r="H9">
         <v>93.10345</v>
       </c>
-      <c r="G9">
-        <v>82.75861999999999</v>
-      </c>
-      <c r="H9">
+      <c r="I9">
         <v>58</v>
-      </c>
-      <c r="I9">
-        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -656,28 +656,28 @@
         </is>
       </c>
       <c r="B10">
+        <v>63.92573</v>
+      </c>
+      <c r="C10">
+        <v>94.91228</v>
+      </c>
+      <c r="D10">
+        <v>81.16437999999999</v>
+      </c>
+      <c r="E10">
+        <v>39.05326</v>
+      </c>
+      <c r="F10">
         <v>64.19098</v>
       </c>
-      <c r="C10">
-        <v>63.92573</v>
-      </c>
-      <c r="D10">
+      <c r="G10">
         <v>101.5789</v>
       </c>
-      <c r="E10">
-        <v>94.91228</v>
-      </c>
-      <c r="F10">
+      <c r="H10">
         <v>96.91781</v>
       </c>
-      <c r="G10">
-        <v>81.16437999999999</v>
-      </c>
-      <c r="H10">
+      <c r="I10">
         <v>56.80473</v>
-      </c>
-      <c r="I10">
-        <v>39.05326</v>
       </c>
     </row>
     <row r="11">
@@ -687,28 +687,28 @@
         </is>
       </c>
       <c r="B11">
+        <v>78.10651</v>
+      </c>
+      <c r="C11">
+        <v>95.56451</v>
+      </c>
+      <c r="D11">
+        <v>81.61765</v>
+      </c>
+      <c r="E11">
+        <v>31.88406</v>
+      </c>
+      <c r="F11">
         <v>78.69823</v>
       </c>
-      <c r="C11">
-        <v>78.10651</v>
-      </c>
-      <c r="D11">
+      <c r="G11">
         <v>100.4032</v>
       </c>
-      <c r="E11">
-        <v>95.56451</v>
-      </c>
-      <c r="F11">
+      <c r="H11">
         <v>95.58823</v>
       </c>
-      <c r="G11">
-        <v>81.61765</v>
-      </c>
-      <c r="H11">
+      <c r="I11">
         <v>47.82609</v>
-      </c>
-      <c r="I11">
-        <v>31.88406</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_aysen.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_aysen.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 19:41</t>
+    <t xml:space="preserve">2026-08-02 19:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_aysen.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_aysen.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-02 19:40</t>
+    <t xml:space="preserve">2026-08-05 10:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_aysen.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_aysen.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 10:33</t>
+    <t xml:space="preserve">2026-08-16 09:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_aysen.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_aysen.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 09:45</t>
+    <t xml:space="preserve">2026-08-19 11:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_aysen.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_aysen.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 11:39</t>
+    <t xml:space="preserve">2026-08-28 11:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_aysen.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_aysen.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:22</t>
+    <t xml:space="preserve">2026-09-06 17:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
